--- a/resources/tools/wordlist_E-J/lessons/lesson-16.xlsx
+++ b/resources/tools/wordlist_E-J/lessons/lesson-16.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B117"/>
+  <dimension ref="A1:B122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,115 +436,115 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>駅員|えきいん（さん）</t>
+          <t>駅員（さん）|えきいん（さん）</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>size</t>
+          <t>parent</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>大きさ|おおきさ</t>
+          <t>親|おや</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>parent</t>
+          <t>relatives</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>親|おや</t>
+          <t>親せき|しんせき</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>final examination</t>
+          <t>garbage</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>期末試験|きまつしけん</t>
+          <t>ごみ</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>research</t>
+          <t>sugar</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>研究|けんきゅう</t>
+          <t>砂糖|さとう</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>garbage</t>
+          <t>file folder; portfolio; file</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ごみ</t>
+          <t>ファイル</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>sugar</t>
+          <t>size</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>砂糖|さとう</t>
+          <t>大きさ|おおきさ</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>scholarship</t>
+          <t>way; road; directions</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>奨学金|しょうがくきん</t>
+          <t>道|みち</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>relatives</t>
+          <t>final examination</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>親せき|しんせき</t>
+          <t>期末試験|きまつしけん</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>letter of recommendation</t>
+          <t>research</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>推薦状|すいせんじょう</t>
+          <t>研究|けんきゅう</t>
         </is>
       </c>
     </row>
@@ -563,175 +563,175 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>typhoon</t>
+          <t>scholarship</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>台風|たいふう</t>
+          <t>奨学金|しょうがくきん</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>day</t>
+          <t>letter of recommendation</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>日|ひ</t>
+          <t>推薦状|すいせんじょう</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>file; portfolio</t>
+          <t>typhoon</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ファイル</t>
+          <t>台風|たいふう</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>way; road; directions</t>
+          <t>culture</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>道|みち</t>
+          <t>文化|ぶんか</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>alarm clock</t>
+          <t>reply</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>目覚まし時計|めざましどけい</t>
+          <t>返事|へんじ</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>dirty</t>
+          <t>day</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>汚い|きたない</t>
+          <t>日|ひ</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>to wake (someone) up</t>
+          <t>dirty</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>起こす|おこす</t>
+          <t>汚い|きたない</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>to treat (someone) to a meal</t>
+          <t>to wake (someone) up (～を)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>おごる</t>
+          <t>起こす|おこす</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>to get depressed</t>
+          <t>to treat (someone) to a meal (person に meal を)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>落ち込む|おちこむ</t>
+          <t>おごる</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>to have difficulty</t>
+          <t>to laugh</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>困る|こまる</t>
+          <t>笑う|わらう</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>to take (something) out; to hand in (something)</t>
+          <t>to get depressed</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>出す|だす</t>
+          <t>落ち込む|おちこむ</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>to take (someone) to (a place)</t>
+          <t>to have difficulty</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>連れていく|つれていく</t>
+          <t>困る|こまる</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>to correct; to fix</t>
+          <t>to take (something) out; to hand in (something) (～を)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>直す|なおす</t>
+          <t>出す|だす</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>to become lost; to lose one's way</t>
+          <t>to correct; to fix (～を)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>道に迷う|みちにまよう</t>
+          <t>直す|なおす</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>to be found</t>
+          <t>to be found (～が)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -743,91 +743,91 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>to go to pick up</t>
+          <t>to translate (source を target に)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>迎えに行く|むかえにいく</t>
+          <t>訳す|やくす</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>to translate</t>
+          <t>to lend (person に thing を)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>訳す|やくす</t>
+          <t>貸す|かす</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>to laugh</t>
+          <t>to take (someone) to (a place) (person を place に)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>笑う|わらう</t>
+          <t>連れていく|つれていく</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>to iron (clothes)</t>
+          <t>to become lost; to lose one's way</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>アイロンをかける</t>
+          <t>道に迷う|みちにまよう</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>to collect</t>
+          <t>to go to pick up (place まで/に person を)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>集める|あつめる</t>
+          <t>迎えに行く|むかえにいく</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>to put (something) in</t>
+          <t>to collect (～を)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>入れる|いれる</t>
+          <t>集める|あつめる</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>to miss (a train, bus, etc.)</t>
+          <t>to put (something) in (thing を place に)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>乗り遅れる|のりおくれる</t>
+          <t>入れる|いれる</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>to show</t>
+          <t>to show (person に thing を)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -839,108 +839,108 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>to oversleep</t>
+          <t>to miss (a train, bus, etc.) (～に)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>朝寝坊する|あさねぼうする</t>
+          <t>乗り遅れる|のりおくれる</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>to show (someone) around</t>
+          <t>to iron (clothes) (～に)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>案内する|あんないする</t>
+          <t>アイロンをかける</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>to explain</t>
+          <t>to oversleep</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>説明する|せつめいする</t>
+          <t>朝寝坊する|あさねぼうする</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>to come to pick up</t>
+          <t>to show (someone) around (place を)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>迎えに来る|むかえにくる</t>
+          <t>案内する|あんないする</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>well...; let me see...</t>
+          <t>to explain</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>ええと</t>
+          <t>説明する|せつめいする</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>by the end of the day</t>
+          <t>to come to pick up (place まで/に person を)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>今日中に|きょうじゅうに</t>
+          <t>迎えに来る|むかえにくる</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>the other day</t>
+          <t>by the end of today</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>この間|このあいだ</t>
+          <t>今日中に|きょうじゅうに</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>about this much</t>
+          <t>in class; during the class</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>このぐらい</t>
+          <t>授業中に|じゅぎょうちゅうに</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>I'm sorry. (casual)</t>
+          <t>the other day</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ごめん</t>
+          <t>この間|このあいだ</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Excuse me.; Sorry to interrupt you.</t>
+          <t>about this much</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>失礼します|しつれいします</t>
+          <t>このぐらい</t>
         </is>
       </c>
     </row>
@@ -983,420 +983,420 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>in class; during the class</t>
+          <t>other</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>授業中に|じゅぎょうちゅうに</t>
+          <t>ほかの</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>well...; let me see...</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ほかの</t>
+          <t>ええと</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>child</t>
+          <t>actually; in fact</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>子供|こども</t>
+          <t>実は|じつは</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>to offer; to sacrifice</t>
+          <t>other than...</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>供える|そなえる</t>
+          <t>～以外|～いがい</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>offer</t>
+          <t>I'm sorry. (casual)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>提供|ていきょう</t>
+          <t>ごめん</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>the world</t>
+          <t>Excuse me.; Sorry to interrupt you.</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>世界|せかい</t>
+          <t>失礼します|しつれいします</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>care</t>
+          <t>child</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>世話|せわ</t>
+          <t>子供|こども</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>generation</t>
+          <t>to offer something to a spirit</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>世代|せだい</t>
+          <t>供える|そなえる</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>the third generation</t>
+          <t>offer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>三世|さんせい</t>
+          <t>提供|ていきょう</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>the society</t>
+          <t>the world</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>世の中|よのなか</t>
+          <t>世界|せかい</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>visibility</t>
+          <t>care</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>視界|しかい</t>
+          <t>世話|せわ</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>political world</t>
+          <t>generation</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>政界|せいかい</t>
+          <t>世代|せだい</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>limit</t>
+          <t>the third generation</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>限界|げんかい</t>
+          <t>三世|さんせい</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>all; entire</t>
+          <t>society</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>全部|ぜんぶ</t>
+          <t>世の中|よのなか</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>safety</t>
+          <t>visibility</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>安全|あんぜん</t>
+          <t>視界|しかい</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>whole country</t>
+          <t>political world</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>全国|ぜんこく</t>
+          <t>政界|せいかい</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>entirely</t>
+          <t>limit</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>全く|まったく</t>
+          <t>限界|げんかい</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>everything; all</t>
+          <t>all; entire</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>全て|すべて</t>
+          <t>全部|ぜんぶ</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>room</t>
+          <t>safety</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>部屋|へや</t>
+          <t>安全|あんぜん</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>tennis club</t>
+          <t>whole country</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>テニス部|テニスぶ</t>
+          <t>全国|ぜんこく</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>department manager</t>
+          <t>entirely</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>部長|ぶちょう</t>
+          <t>全く|まったく</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>(something) begins</t>
+          <t>everything; all</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>始まる|はじまる</t>
+          <t>全て|すべて</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>to begin (something)</t>
+          <t>all; entire</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>始める|はじめる</t>
+          <t>全部|ぜんぶ</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>first train</t>
+          <t>room</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>始発|しはつ</t>
+          <t>部屋|へや</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>start</t>
+          <t>tennis club</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>開始|かいし</t>
+          <t>テニス部|テニスぶ</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>every week</t>
+          <t>department manager</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>毎週|まいしゅう</t>
+          <t>部長|ぶちょう</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>last week</t>
+          <t>(something) begins</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>先週|せんしゅう</t>
+          <t>始まる|はじまる</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>one week</t>
+          <t>to begin (something)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>一週間|いっしゅうかん</t>
+          <t>始める|はじめる</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>second week</t>
+          <t>first train (of the day)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>二週目|にしゅうめ</t>
+          <t>始発|しはつ</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>weekend</t>
+          <t>start</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>週末|しゅうまつ</t>
+          <t>開始|かいし</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>other than...</t>
+          <t>every week</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>～以外|～いがい</t>
+          <t>毎週|まいしゅう</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>...or more</t>
+          <t>last week</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>～以上|～いじょう</t>
+          <t>先週|せんしゅう</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>...or less</t>
+          <t>one week</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>～以下|～いか</t>
+          <t>一週間|いっしゅうかん</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>within...</t>
+          <t>second week</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>～以内|～いない</t>
+          <t>二週目|にしゅうめ</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>before; formerly</t>
+          <t>weekend</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>以前|いぜん</t>
+          <t>週末|しゅうまつ</t>
         </is>
       </c>
     </row>
@@ -1559,7 +1559,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>person on one's side</t>
+          <t>ally; person on one's side</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -1817,6 +1817,66 @@
       <c r="B117" t="inlineStr">
         <is>
           <t>待合室|まちあいしつ</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>other than...</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>～以外|～いがい</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>...or more</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>～以上|～いじょう</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>...or less</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>～以下|～いか</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>within...</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>～以内|～いない</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>before; formerly</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>以前|いぜん</t>
         </is>
       </c>
     </row>
